--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -2349,7 +2349,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46272.16623265046</v>
+        <v>46279.1692025463</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46272.16623270833</v>
+        <v>46279.1692037037</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46272.16623267361</v>
+        <v>46279.169199745374</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>73</v>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46272.16623268518</v>
+        <v>46279.16920153935</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="326">
   <si>
     <t xml:space="preserve"> 50001585 - TENIENTE - CODELCO</t>
   </si>
@@ -286,9 +286,6 @@
   </si>
   <si>
     <t>Generación OC corte laser   ot 4385- 4386,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -2349,7 +2346,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46279.1692025463</v>
+        <v>46280.12614212963</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2393,29 +2390,29 @@
       <c r="R15" s="9">
         <v>46276</v>
       </c>
-      <c r="S15" s="12" t="s">
-        <v>67</v>
+      <c r="S15" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="T15" s="10">
         <v>0</v>
       </c>
       <c r="U15" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
         <v>46232.83579084491</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46279.1692037037</v>
+        <v>46280.12614209491</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2448,7 +2445,7 @@
         <v>65</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46279</v>
@@ -2456,29 +2453,29 @@
       <c r="R16" s="5">
         <v>46276</v>
       </c>
-      <c r="S16" s="12" t="s">
-        <v>67</v>
+      <c r="S16" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="T16" s="6">
         <v>0</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" s="9">
         <v>46232.83579519676</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46279.169199745374</v>
+        <v>46280.12614228009</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2511,7 +2508,7 @@
         <v>65</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="9">
         <v>46279</v>
@@ -2519,29 +2516,29 @@
       <c r="R17" s="9">
         <v>46276</v>
       </c>
-      <c r="S17" s="12" t="s">
-        <v>67</v>
+      <c r="S17" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
       <c r="U17" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46232.83579891204</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46279.16920153935</v>
+        <v>46280.126142106485</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2574,7 +2571,7 @@
         <v>65</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q18" s="5">
         <v>46279</v>
@@ -2582,19 +2579,19 @@
       <c r="R18" s="5">
         <v>46276</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>67</v>
+      <c r="S18" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" s="9">
         <v>46232.8586305787</v>
@@ -2639,7 +2636,7 @@
         <v>44</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q19" s="9">
         <v>46239</v>
@@ -2659,7 +2656,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" s="5">
         <v>46232.83564635417</v>
@@ -2669,7 +2666,7 @@
         <v>46233.639479722224</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2693,7 +2690,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2706,7 +2703,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" s="9">
         <v>46232.83580497685</v>
@@ -2716,16 +2713,16 @@
         <v>46252.60280438657</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="I21" s="9">
         <v>46280</v>
@@ -2743,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q21" s="9">
         <v>46290</v>
@@ -2764,12 +2761,12 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B22" s="5">
         <v>46232.835810578705</v>
@@ -2779,16 +2776,16 @@
         <v>46233.651251539355</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I22" s="5">
         <v>46280</v>
@@ -2806,13 +2803,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -2823,12 +2820,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B23" s="9">
         <v>46232.83581497685</v>
@@ -2838,16 +2835,16 @@
         <v>46233.651247037036</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="I23" s="9">
         <v>46282</v>
@@ -2865,13 +2862,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2882,12 +2879,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
         <v>46232.835819618056</v>
@@ -2897,16 +2894,16 @@
         <v>46252.602819155094</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I24" s="5">
         <v>46280</v>
@@ -2924,10 +2921,10 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2945,12 +2942,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B25" s="9">
         <v>46232.83582385417</v>
@@ -2960,16 +2957,16 @@
         <v>46233.651424247684</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="I25" s="9">
         <v>46280</v>
@@ -2987,13 +2984,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3003,7 +3000,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46232.835827523144</v>
@@ -3013,16 +3010,16 @@
         <v>46233.651529675924</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I26" s="5">
         <v>46282</v>
@@ -3040,13 +3037,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3056,7 +3053,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="9">
         <v>46232.83583092593</v>
@@ -3066,16 +3063,16 @@
         <v>46252.602839178246</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="I27" s="9">
         <v>46280</v>
@@ -3093,10 +3090,10 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3114,12 +3111,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46232.83583467593</v>
@@ -3129,16 +3126,16 @@
         <v>46240.823460775464</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I28" s="5">
         <v>46280</v>
@@ -3156,13 +3153,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3172,7 +3169,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B29" s="9">
         <v>46232.83583809028</v>
@@ -3182,16 +3179,16 @@
         <v>46240.82345635416</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="I29" s="9">
         <v>46282</v>
@@ -3209,13 +3206,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3225,7 +3222,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5">
         <v>46232.835841458334</v>
@@ -3235,16 +3232,16 @@
         <v>46252.602874247685</v>
       </c>
       <c r="E30" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="6" t="s">
+      <c r="H30" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="I30" s="5">
         <v>46280</v>
@@ -3262,10 +3259,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3283,12 +3280,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B31" s="9">
         <v>46232.83584547453</v>
@@ -3298,16 +3295,16 @@
         <v>46255.628654224536</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>112</v>
       </c>
       <c r="I31" s="9">
         <v>46280</v>
@@ -3325,13 +3322,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O31" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="P31" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="P31" s="10" t="s">
-        <v>117</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3341,7 +3338,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46232.83584972222</v>
@@ -3351,16 +3348,16 @@
         <v>46233.652321284724</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="I32" s="5">
         <v>46290</v>
@@ -3378,13 +3375,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3394,7 +3391,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B33" s="9">
         <v>46232.83585321759</v>
@@ -3404,16 +3401,16 @@
         <v>46233.65237416667</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I33" s="9">
         <v>46321</v>
@@ -3431,13 +3428,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3447,7 +3444,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46232.85014579861</v>
@@ -3457,16 +3454,16 @@
         <v>46252.60289347223</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46240</v>
@@ -3484,10 +3481,10 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3505,12 +3502,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B35" s="9">
         <v>46232.85120104167</v>
@@ -3522,16 +3519,16 @@
         <v>46233.907791053236</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="I35" s="9">
         <v>46240</v>
@@ -3549,13 +3546,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>45</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3565,7 +3562,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46232.85127679398</v>
@@ -3575,16 +3572,16 @@
         <v>46233.90779653935</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I36" s="5">
         <v>46259</v>
@@ -3602,13 +3599,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3618,7 +3615,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="9">
         <v>46232.85132364584</v>
@@ -3630,16 +3627,16 @@
         <v>46233.90783645833</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="I37" s="9">
         <v>46230</v>
@@ -3657,10 +3654,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -3673,7 +3670,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B38" s="5">
         <v>46232.83589858796</v>
@@ -3683,7 +3680,7 @@
         <v>46261.48903378472</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>25</v>
@@ -3707,7 +3704,7 @@
         <v>26</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3720,7 +3717,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B39" s="9">
         <v>46232.83590302084</v>
@@ -3732,16 +3729,16 @@
         <v>46261.48904716435</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -3759,13 +3756,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O39" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="P39" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="P39" s="10" t="s">
-        <v>145</v>
       </c>
       <c r="Q39" s="9">
         <v>46245</v>
@@ -3785,7 +3782,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46232.83591185186</v>
@@ -3797,16 +3794,16 @@
         <v>46260.67723627315</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46239</v>
@@ -3824,13 +3821,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>42</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3840,7 +3837,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B41" s="9">
         <v>46232.83591513889</v>
@@ -3850,16 +3847,16 @@
         <v>46275.162032314816</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="I41" s="9">
         <v>46268</v>
@@ -3877,13 +3874,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O41" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="P41" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="P41" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="Q41" s="9">
         <v>46274</v>
@@ -3898,12 +3895,12 @@
         <v>0</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46232.83592324074</v>
@@ -3913,16 +3910,16 @@
         <v>46274.16881178241</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I42" s="5">
         <v>46268</v>
@@ -3940,13 +3937,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3956,7 +3953,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="9">
         <v>46232.83592622685</v>
@@ -3972,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I43" s="9">
         <v>46275</v>
@@ -3993,13 +3990,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O43" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="P43" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="P43" s="10" t="s">
-        <v>157</v>
       </c>
       <c r="Q43" s="9">
         <v>46275</v>
@@ -4014,12 +4011,12 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46232.83594902778</v>
@@ -4029,16 +4026,16 @@
         <v>46275.1687925</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I44" s="5">
         <v>46275</v>
@@ -4059,7 +4056,7 @@
         <v>65</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>65</v>
@@ -4072,7 +4069,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B45" s="9">
         <v>46232.83595255787</v>
@@ -4082,16 +4079,16 @@
         <v>46260.679872256944</v>
       </c>
       <c r="E45" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I45" s="9">
         <v>46356</v>
@@ -4109,13 +4106,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q45" s="9">
         <v>46356</v>
@@ -4130,12 +4127,12 @@
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46232.83600618056</v>
@@ -4145,16 +4142,16 @@
         <v>46240.82426292824</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I46" s="5">
         <v>46356</v>
@@ -4172,13 +4169,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4188,7 +4185,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B47" s="9">
         <v>46232.83600939815</v>
@@ -4198,16 +4195,16 @@
         <v>46240.824259375004</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I47" s="9">
         <v>46356</v>
@@ -4225,13 +4222,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4241,7 +4238,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B48" s="5">
         <v>46232.83601267361</v>
@@ -4251,16 +4248,16 @@
         <v>46240.824255416665</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I48" s="5">
         <v>46356</v>
@@ -4278,13 +4275,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4294,7 +4291,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B49" s="9">
         <v>46232.83601601852</v>
@@ -4304,16 +4301,16 @@
         <v>46240.8242518287</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I49" s="9">
         <v>46356</v>
@@ -4331,13 +4328,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4347,7 +4344,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B50" s="5">
         <v>46232.83611833333</v>
@@ -4357,7 +4354,7 @@
         <v>46233.641839375</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4381,7 +4378,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4394,7 +4391,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B51" s="9">
         <v>46232.836122465276</v>
@@ -4404,16 +4401,16 @@
         <v>46260.67989972222</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
+      <c r="H51" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="I51" s="9">
         <v>46293</v>
@@ -4431,13 +4428,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q51" s="9">
         <v>46294</v>
@@ -4452,12 +4449,12 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B52" s="5">
         <v>46232.83612731482</v>
@@ -4467,16 +4464,16 @@
         <v>46260.679925335644</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="I52" s="5">
         <v>46293</v>
@@ -4494,13 +4491,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q52" s="5">
         <v>46294</v>
@@ -4515,12 +4512,12 @@
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B53" s="9">
         <v>46232.83613222222</v>
@@ -4530,16 +4527,16 @@
         <v>46260.679949259254</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="I53" s="9">
         <v>46293</v>
@@ -4557,13 +4554,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q53" s="9">
         <v>46294</v>
@@ -4578,12 +4575,12 @@
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B54" s="5">
         <v>46232.836136909726</v>
@@ -4593,16 +4590,16 @@
         <v>46260.68020320602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I54" s="5">
         <v>46295</v>
@@ -4620,13 +4617,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q54" s="5">
         <v>46295</v>
@@ -4641,12 +4638,12 @@
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B55" s="9">
         <v>46232.83614177084</v>
@@ -4656,16 +4653,16 @@
         <v>46260.6802031713</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I55" s="9">
         <v>46295</v>
@@ -4683,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q55" s="9">
         <v>46295</v>
@@ -4704,12 +4701,12 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B56" s="5">
         <v>46232.83614663195</v>
@@ -4719,16 +4716,16 @@
         <v>46260.68020337963</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I56" s="5">
         <v>46295</v>
@@ -4746,13 +4743,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q56" s="5">
         <v>46295</v>
@@ -4767,12 +4764,12 @@
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B57" s="9">
         <v>46232.83615094908</v>
@@ -4782,7 +4779,7 @@
         <v>46233.64318932871</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4806,7 +4803,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4819,7 +4816,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B58" s="5">
         <v>46232.83615418982</v>
@@ -4829,16 +4826,16 @@
         <v>46260.68026579861</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I58" s="5">
         <v>46296</v>
@@ -4856,13 +4853,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q58" s="5">
         <v>46304</v>
@@ -4877,12 +4874,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B59" s="9">
         <v>46232.83616251158</v>
@@ -4892,16 +4889,16 @@
         <v>46260.680265891206</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I59" s="9">
         <v>46307</v>
@@ -4919,13 +4916,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q59" s="9">
         <v>46324</v>
@@ -4940,12 +4937,12 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B60" s="5">
         <v>46232.83619825232</v>
@@ -4955,16 +4952,16 @@
         <v>46233.64356575231</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I60" s="5">
         <v>46307</v>
@@ -4982,13 +4979,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4998,7 +4995,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B61" s="9">
         <v>46232.8362028125</v>
@@ -5008,16 +5005,16 @@
         <v>46233.643566342595</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I61" s="9">
         <v>46307</v>
@@ -5035,13 +5032,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5051,7 +5048,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B62" s="5">
         <v>46232.83620730324</v>
@@ -5061,16 +5058,16 @@
         <v>46233.643566956016</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I62" s="5">
         <v>46307</v>
@@ -5088,13 +5085,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5104,7 +5101,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B63" s="9">
         <v>46232.83621217593</v>
@@ -5114,16 +5111,16 @@
         <v>46233.6435675463</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I63" s="9">
         <v>46307</v>
@@ -5141,13 +5138,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5157,7 +5154,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B64" s="5">
         <v>46232.836342152776</v>
@@ -5167,16 +5164,16 @@
         <v>46260.68039708333</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I64" s="5">
         <v>46325</v>
@@ -5194,13 +5191,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q64" s="5">
         <v>46328</v>
@@ -5215,12 +5212,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B65" s="9">
         <v>46232.83637209491</v>
@@ -5230,16 +5227,16 @@
         <v>46233.643859131946</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I65" s="9">
         <v>46325</v>
@@ -5257,13 +5254,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5273,7 +5270,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B66" s="5">
         <v>46232.836376666666</v>
@@ -5283,16 +5280,16 @@
         <v>46233.64385857639</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I66" s="5">
         <v>46325</v>
@@ -5310,13 +5307,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5326,7 +5323,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B67" s="9">
         <v>46232.836381319445</v>
@@ -5336,16 +5333,16 @@
         <v>46233.6438580324</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I67" s="9">
         <v>46325</v>
@@ -5363,13 +5360,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5379,7 +5376,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B68" s="5">
         <v>46232.83638501157</v>
@@ -5389,16 +5386,16 @@
         <v>46233.64385685185</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I68" s="5">
         <v>46325</v>
@@ -5416,13 +5413,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5432,7 +5429,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B69" s="9">
         <v>46232.836502499995</v>
@@ -5442,7 +5439,7 @@
         <v>46233.64467054398</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>25</v>
@@ -5466,7 +5463,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>26</v>
@@ -5479,7 +5476,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B70" s="5">
         <v>46232.83650636574</v>
@@ -5489,16 +5486,16 @@
         <v>46260.68082252315</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="I70" s="5">
         <v>46239</v>
@@ -5516,13 +5513,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>54</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q70" s="5">
         <v>46240</v>
@@ -5537,12 +5534,12 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B71" s="9">
         <v>46232.836519247685</v>
@@ -5552,16 +5549,16 @@
         <v>46260.68090866898</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="I71" s="9">
         <v>46239</v>
@@ -5579,13 +5576,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>59</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q71" s="9">
         <v>46240</v>
@@ -5600,12 +5597,12 @@
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B72" s="5">
         <v>46232.83652788194</v>
@@ -5615,16 +5612,16 @@
         <v>46260.680964652776</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="I72" s="5">
         <v>46343</v>
@@ -5642,13 +5639,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q72" s="5">
         <v>46344</v>
@@ -5663,12 +5660,12 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B73" s="9">
         <v>46232.83654054398</v>
@@ -5678,7 +5675,7 @@
         <v>46233.645743333334</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>25</v>
@@ -5702,7 +5699,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5715,7 +5712,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B74" s="5">
         <v>46232.83654375</v>
@@ -5725,7 +5722,7 @@
         <v>46260.68063219907</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5752,13 +5749,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q74" s="5">
         <v>46346</v>
@@ -5773,12 +5770,12 @@
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B75" s="9">
         <v>46232.836570162035</v>
@@ -5788,7 +5785,7 @@
         <v>46233.65450737269</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5815,13 +5812,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5831,7 +5828,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B76" s="5">
         <v>46232.83657339121</v>
@@ -5841,7 +5838,7 @@
         <v>46260.680678715275</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5868,13 +5865,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5884,7 +5881,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B77" s="9">
         <v>46232.83657665509</v>
@@ -5894,7 +5891,7 @@
         <v>46233.65449428241</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5921,13 +5918,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5937,7 +5934,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B78" s="5">
         <v>46232.83658011574</v>
@@ -5947,7 +5944,7 @@
         <v>46233.65449056713</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5974,13 +5971,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5990,7 +5987,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B79" s="9">
         <v>46232.83664298611</v>
@@ -6000,7 +5997,7 @@
         <v>46260.681952962965</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6027,13 +6024,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q79" s="9">
         <v>46349</v>
@@ -6048,12 +6045,12 @@
         <v>0</v>
       </c>
       <c r="U79" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B80" s="5">
         <v>46232.8367334375</v>
@@ -6063,7 +6060,7 @@
         <v>46233.65465295139</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6090,13 +6087,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O80" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>241</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6106,7 +6103,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B81" s="9">
         <v>46232.83673865741</v>
@@ -6116,7 +6113,7 @@
         <v>46233.65464978009</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6143,13 +6140,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O81" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="P81" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="P81" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6159,7 +6156,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B82" s="5">
         <v>46232.83674337963</v>
@@ -6169,7 +6166,7 @@
         <v>46233.65464680556</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6196,13 +6193,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6212,7 +6209,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B83" s="9">
         <v>46232.83674840278</v>
@@ -6222,7 +6219,7 @@
         <v>46233.65464278935</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6249,13 +6246,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O83" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="P83" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6265,7 +6262,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B84" s="5">
         <v>46232.836891377316</v>
@@ -6275,7 +6272,7 @@
         <v>46260.68198707176</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6302,13 +6299,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q84" s="5">
         <v>46350</v>
@@ -6323,12 +6320,12 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B85" s="9">
         <v>46232.836924375</v>
@@ -6338,7 +6335,7 @@
         <v>46233.65478820602</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6365,13 +6362,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6381,7 +6378,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B86" s="5">
         <v>46232.836927488424</v>
@@ -6391,7 +6388,7 @@
         <v>46233.65478517361</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6418,13 +6415,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6434,7 +6431,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B87" s="9">
         <v>46232.836930474536</v>
@@ -6444,7 +6441,7 @@
         <v>46233.654781273144</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6471,13 +6468,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6487,7 +6484,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B88" s="5">
         <v>46232.836933530096</v>
@@ -6497,7 +6494,7 @@
         <v>46233.65477793981</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6524,13 +6521,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6540,7 +6537,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B89" s="9">
         <v>46232.836990428244</v>
@@ -6550,7 +6547,7 @@
         <v>46260.68201387732</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6577,13 +6574,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q89" s="9">
         <v>46351</v>
@@ -6598,12 +6595,12 @@
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B90" s="5">
         <v>46232.83702368056</v>
@@ -6613,7 +6610,7 @@
         <v>46233.65523672454</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6640,13 +6637,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6656,7 +6653,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B91" s="9">
         <v>46232.837026863424</v>
@@ -6666,7 +6663,7 @@
         <v>46233.655233032405</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6693,13 +6690,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6709,7 +6706,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B92" s="5">
         <v>46232.83702931713</v>
@@ -6719,7 +6716,7 @@
         <v>46233.655229537035</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6746,13 +6743,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6762,7 +6759,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B93" s="9">
         <v>46232.83703243056</v>
@@ -6772,7 +6769,7 @@
         <v>46233.655226435185</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6799,13 +6796,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6815,7 +6812,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B94" s="5">
         <v>46232.83713237269</v>
@@ -6825,7 +6822,7 @@
         <v>46260.682038240746</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6852,13 +6849,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q94" s="5">
         <v>46352</v>
@@ -6873,12 +6870,12 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B95" s="9">
         <v>46232.83715663194</v>
@@ -6888,7 +6885,7 @@
         <v>46233.655363067126</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6915,13 +6912,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6931,7 +6928,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B96" s="5">
         <v>46232.83715961805</v>
@@ -6941,7 +6938,7 @@
         <v>46233.65535960648</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6968,13 +6965,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6984,7 +6981,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B97" s="9">
         <v>46232.83716207176</v>
@@ -6994,7 +6991,7 @@
         <v>46233.65535680555</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7021,13 +7018,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7037,7 +7034,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B98" s="5">
         <v>46232.837165324076</v>
@@ -7047,7 +7044,7 @@
         <v>46233.65534453704</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7074,13 +7071,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7090,7 +7087,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B99" s="9">
         <v>46232.837259120366</v>
@@ -7100,7 +7097,7 @@
         <v>46260.68206168982</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7127,10 +7124,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7148,12 +7145,12 @@
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B100" s="5">
         <v>46232.837293495366</v>
@@ -7163,7 +7160,7 @@
         <v>46233.655496747684</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7190,13 +7187,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7206,7 +7203,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B101" s="9">
         <v>46232.83729747686</v>
@@ -7216,7 +7213,7 @@
         <v>46233.65549366898</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7243,13 +7240,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7259,7 +7256,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B102" s="5">
         <v>46232.83730121527</v>
@@ -7269,7 +7266,7 @@
         <v>46233.65549012732</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7296,13 +7293,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7312,7 +7309,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B103" s="9">
         <v>46232.83730554398</v>
@@ -7322,7 +7319,7 @@
         <v>46233.65548677083</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7349,13 +7346,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7365,7 +7362,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B104" s="5">
         <v>46232.83737395833</v>
@@ -7375,7 +7372,7 @@
         <v>46260.68208619213</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7402,10 +7399,10 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>26</v>
@@ -7423,12 +7420,12 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B105" s="9">
         <v>46232.83744990741</v>
@@ -7438,7 +7435,7 @@
         <v>46233.65578177084</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7465,13 +7462,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7481,7 +7478,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B106" s="5">
         <v>46232.83745327547</v>
@@ -7491,7 +7488,7 @@
         <v>46233.65578223379</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7518,13 +7515,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7534,7 +7531,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B107" s="9">
         <v>46232.837456712965</v>
@@ -7544,7 +7541,7 @@
         <v>46233.65578273148</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7571,13 +7568,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7587,7 +7584,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B108" s="5">
         <v>46232.83746033565</v>
@@ -7597,7 +7594,7 @@
         <v>46233.65578320602</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7624,13 +7621,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7640,7 +7637,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B109" s="9">
         <v>46232.837520092595</v>
@@ -7650,7 +7647,7 @@
         <v>46233.64911908565</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>25</v>
@@ -7674,7 +7671,7 @@
         <v>26</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>26</v>
@@ -7687,7 +7684,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B110" s="5">
         <v>46232.837524166665</v>
@@ -7697,16 +7694,16 @@
         <v>46260.68212885417</v>
       </c>
       <c r="E110" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G110" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="F110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G110" s="6" t="s">
+      <c r="H110" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="I110" s="5">
         <v>46359</v>
@@ -7724,13 +7721,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q110" s="5">
         <v>46359</v>
@@ -7745,12 +7742,12 @@
         <v>0</v>
       </c>
       <c r="U110" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B111" s="9">
         <v>46232.83755571759</v>
@@ -7760,16 +7757,16 @@
         <v>46233.65598135417</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>287</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="I111" s="9">
         <v>46359</v>
@@ -7787,13 +7784,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7803,7 +7800,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B112" s="5">
         <v>46232.837559548614</v>
@@ -7813,16 +7810,16 @@
         <v>46233.65597814815</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="I112" s="5">
         <v>46359</v>
@@ -7840,13 +7837,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7856,7 +7853,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B113" s="9">
         <v>46232.83756364584</v>
@@ -7866,16 +7863,16 @@
         <v>46233.65597451389</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>287</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="I113" s="9">
         <v>46359</v>
@@ -7893,13 +7890,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7909,7 +7906,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B114" s="5">
         <v>46232.83756778935</v>
@@ -7919,16 +7916,16 @@
         <v>46233.65597096065</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="I114" s="5">
         <v>46359</v>
@@ -7946,13 +7943,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -7962,7 +7959,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B115" s="9">
         <v>46232.83768009259</v>
@@ -7972,7 +7969,7 @@
         <v>46260.68216930555</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -7999,10 +7996,10 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8020,12 +8017,12 @@
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B116" s="5">
         <v>46232.837703680554</v>
@@ -8035,7 +8032,7 @@
         <v>46233.656983611116</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8062,13 +8059,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8078,7 +8075,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B117" s="9">
         <v>46232.837707175924</v>
@@ -8088,7 +8085,7 @@
         <v>46233.65698048611</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8115,13 +8112,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8131,7 +8128,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B118" s="5">
         <v>46232.837710555556</v>
@@ -8141,7 +8138,7 @@
         <v>46233.65697711805</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8168,13 +8165,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8184,7 +8181,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B119" s="9">
         <v>46232.837713981484</v>
@@ -8194,7 +8191,7 @@
         <v>46233.65697394676</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8221,13 +8218,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8237,7 +8234,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B120" s="5">
         <v>46232.837813125</v>
@@ -8247,16 +8244,16 @@
         <v>46260.68218884259</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I120" s="5">
         <v>46363</v>
@@ -8274,13 +8271,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q120" s="5">
         <v>46363</v>
@@ -8295,12 +8292,12 @@
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B121" s="9">
         <v>46232.83784550926</v>
@@ -8310,16 +8307,16 @@
         <v>46233.65710880787</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H121" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I121" s="9">
         <v>46363</v>
@@ -8337,13 +8334,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8353,7 +8350,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B122" s="5">
         <v>46232.837850254626</v>
@@ -8363,16 +8360,16 @@
         <v>46233.65710540509</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I122" s="5">
         <v>46363</v>
@@ -8390,13 +8387,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8406,7 +8403,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B123" s="9">
         <v>46232.83785502314</v>
@@ -8416,16 +8413,16 @@
         <v>46233.657102268524</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H123" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I123" s="9">
         <v>46363</v>
@@ -8443,13 +8440,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8459,7 +8456,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B124" s="5">
         <v>46232.83785935185</v>
@@ -8469,16 +8466,16 @@
         <v>46233.65709878472</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I124" s="5">
         <v>46363</v>
@@ -8496,13 +8493,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8512,7 +8509,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B125" s="9">
         <v>46232.837973483794</v>
@@ -8522,16 +8519,16 @@
         <v>46260.682238113426</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I125" s="9">
         <v>46364</v>
@@ -8549,13 +8546,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q125" s="9">
         <v>46364</v>
@@ -8570,12 +8567,12 @@
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B126" s="5">
         <v>46232.838005439815</v>
@@ -8585,16 +8582,16 @@
         <v>46233.65729934028</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I126" s="5">
         <v>46364</v>
@@ -8612,13 +8609,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8628,7 +8625,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B127" s="9">
         <v>46232.838009259256</v>
@@ -8638,16 +8635,16 @@
         <v>46233.65729582176</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I127" s="9">
         <v>46364</v>
@@ -8665,13 +8662,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8681,7 +8678,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B128" s="5">
         <v>46232.83801302083</v>
@@ -8691,16 +8688,16 @@
         <v>46233.657292557866</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I128" s="5">
         <v>46364</v>
@@ -8718,13 +8715,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8734,7 +8731,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B129" s="9">
         <v>46232.83801685185</v>
@@ -8744,16 +8741,16 @@
         <v>46233.65728900463</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I129" s="9">
         <v>46364</v>
@@ -8771,13 +8768,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8787,7 +8784,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B130" s="5">
         <v>46232.83807947917</v>
@@ -8797,7 +8794,7 @@
         <v>46233.65049251157</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>25</v>
@@ -8821,7 +8818,7 @@
         <v>26</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>26</v>
@@ -8834,7 +8831,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B131" s="9">
         <v>46232.83808368056</v>
@@ -8844,16 +8841,16 @@
         <v>46260.68180542824</v>
       </c>
       <c r="E131" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="F131" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G131" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="F131" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G131" s="10" t="s">
+      <c r="H131" s="10" t="s">
         <v>323</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>324</v>
       </c>
       <c r="I131" s="9">
         <v>46365</v>
@@ -8871,13 +8868,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q131" s="9">
         <v>46373</v>
@@ -8892,12 +8889,12 @@
         <v>0</v>
       </c>
       <c r="U131" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B132" s="5">
         <v>46232.83812608796</v>
@@ -8907,16 +8904,16 @@
         <v>46260.68180643518</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>324</v>
       </c>
       <c r="I132" s="5">
         <v>46365</v>
@@ -8934,13 +8931,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q132" s="5">
         <v>46373</v>
@@ -8955,7 +8952,7 @@
         <v>0</v>
       </c>
       <c r="U132" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46233.651251539355</v>
+        <v>46281.16872909722</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46233.651424247684</v>
+        <v>46281.16873065972</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>70</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46240.823460775464</v>
+        <v>46281.168731655096</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>76</v>

--- a/data/50001585 - TENIENTE - CODELCO.xlsx
+++ b/data/50001585 - TENIENTE - CODELCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="327">
   <si>
     <t xml:space="preserve"> 50001585 - TENIENTE - CODELCO</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t xml:space="preserve">Generación OC corte laser   ot 4385- 4386,Fabricacion corte laser  ot 4385- 4386 </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1217003777375047</t>
@@ -2710,7 +2713,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46252.60280438657</v>
+        <v>46283.15255828704</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>81</v>
@@ -2754,8 +2757,8 @@
       <c r="R21" s="9">
         <v>46280</v>
       </c>
-      <c r="S21" s="7" t="s">
-        <v>33</v>
+      <c r="S21" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
@@ -2766,7 +2769,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5">
         <v>46232.835810578705</v>
@@ -2776,7 +2779,7 @@
         <v>46281.16872909722</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2809,7 +2812,7 @@
         <v>63</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -2825,7 +2828,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="9">
         <v>46232.83581497685</v>
@@ -2835,7 +2838,7 @@
         <v>46233.651247037036</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2865,10 +2868,10 @@
         <v>81</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2884,17 +2887,17 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46232.835819618056</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46252.602819155094</v>
+        <v>46283.15255820602</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2924,7 +2927,7 @@
         <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2935,8 +2938,8 @@
       <c r="R24" s="5">
         <v>46280</v>
       </c>
-      <c r="S24" s="7" t="s">
-        <v>33</v>
+      <c r="S24" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
@@ -2947,7 +2950,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B25" s="9">
         <v>46232.83582385417</v>
@@ -2984,13 +2987,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3000,7 +3003,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" s="5">
         <v>46232.835827523144</v>
@@ -3010,7 +3013,7 @@
         <v>46233.651529675924</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3037,13 +3040,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3053,17 +3056,17 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="9">
         <v>46232.83583092593</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46252.602839178246</v>
+        <v>46283.152561435185</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3093,7 +3096,7 @@
         <v>80</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>26</v>
@@ -3104,8 +3107,8 @@
       <c r="R27" s="9">
         <v>46280</v>
       </c>
-      <c r="S27" s="7" t="s">
-        <v>33</v>
+      <c r="S27" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
@@ -3116,7 +3119,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>46232.83583467593</v>
@@ -3153,13 +3156,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3169,7 +3172,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B29" s="9">
         <v>46232.83583809028</v>
@@ -3179,7 +3182,7 @@
         <v>46240.82345635416</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3206,13 +3209,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>76</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3222,7 +3225,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" s="5">
         <v>46232.835841458334</v>
@@ -3232,16 +3235,16 @@
         <v>46252.602874247685</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I30" s="5">
         <v>46280</v>
@@ -3262,7 +3265,7 @@
         <v>80</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3285,7 +3288,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" s="9">
         <v>46232.83584547453</v>
@@ -3295,16 +3298,16 @@
         <v>46255.628654224536</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I31" s="9">
         <v>46280</v>
@@ -3322,13 +3325,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3338,7 +3341,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5">
         <v>46232.83584972222</v>
@@ -3348,16 +3351,16 @@
         <v>46233.652321284724</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I32" s="5">
         <v>46290</v>
@@ -3375,13 +3378,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3391,7 +3394,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" s="9">
         <v>46232.83585321759</v>
@@ -3401,16 +3404,16 @@
         <v>46233.65237416667</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I33" s="9">
         <v>46321</v>
@@ -3428,13 +3431,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3444,7 +3447,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46232.85014579861</v>
@@ -3454,16 +3457,16 @@
         <v>46252.60289347223</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46240</v>
@@ -3484,7 +3487,7 @@
         <v>80</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3507,7 +3510,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B35" s="9">
         <v>46232.85120104167</v>
@@ -3525,10 +3528,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I35" s="9">
         <v>46240</v>
@@ -3546,13 +3549,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>45</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3562,7 +3565,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46232.85127679398</v>
@@ -3572,16 +3575,16 @@
         <v>46233.90779653935</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I36" s="5">
         <v>46259</v>
@@ -3599,13 +3602,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3615,7 +3618,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="9">
         <v>46232.85132364584</v>
@@ -3627,16 +3630,16 @@
         <v>46233.90783645833</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I37" s="9">
         <v>46230</v>
@@ -3654,7 +3657,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>78</v>
@@ -3670,7 +3673,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46232.83589858796</v>
@@ -3680,7 +3683,7 @@
         <v>46261.48903378472</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>25</v>
@@ -3704,7 +3707,7 @@
         <v>26</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3717,7 +3720,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B39" s="9">
         <v>46232.83590302084</v>
@@ -3729,16 +3732,16 @@
         <v>46261.48904716435</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -3756,13 +3759,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q39" s="9">
         <v>46245</v>
@@ -3782,7 +3785,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46232.83591185186</v>
@@ -3794,16 +3797,16 @@
         <v>46260.67723627315</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46239</v>
@@ -3821,13 +3824,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>42</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3837,7 +3840,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="9">
         <v>46232.83591513889</v>
@@ -3847,16 +3850,16 @@
         <v>46275.162032314816</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I41" s="9">
         <v>46268</v>
@@ -3874,13 +3877,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="9">
         <v>46274</v>
@@ -3900,7 +3903,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46232.83592324074</v>
@@ -3910,16 +3913,16 @@
         <v>46274.16881178241</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I42" s="5">
         <v>46268</v>
@@ -3937,13 +3940,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3953,7 +3956,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B43" s="9">
         <v>46232.83592622685</v>
@@ -3969,10 +3972,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I43" s="9">
         <v>46275</v>
@@ -3990,13 +3993,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="9">
         <v>46275</v>
@@ -4016,7 +4019,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46232.83594902778</v>
@@ -4026,16 +4029,16 @@
         <v>46275.1687925</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I44" s="5">
         <v>46275</v>
@@ -4056,7 +4059,7 @@
         <v>65</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>65</v>
@@ -4069,7 +4072,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B45" s="9">
         <v>46232.83595255787</v>
@@ -4079,16 +4082,16 @@
         <v>46260.679872256944</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I45" s="9">
         <v>46356</v>
@@ -4106,13 +4109,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q45" s="9">
         <v>46356</v>
@@ -4132,7 +4135,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46232.83600618056</v>
@@ -4142,16 +4145,16 @@
         <v>46240.82426292824</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I46" s="5">
         <v>46356</v>
@@ -4169,13 +4172,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4185,7 +4188,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B47" s="9">
         <v>46232.83600939815</v>
@@ -4195,16 +4198,16 @@
         <v>46240.824259375004</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I47" s="9">
         <v>46356</v>
@@ -4222,13 +4225,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4238,7 +4241,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B48" s="5">
         <v>46232.83601267361</v>
@@ -4248,16 +4251,16 @@
         <v>46240.824255416665</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I48" s="5">
         <v>46356</v>
@@ -4275,13 +4278,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4291,7 +4294,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B49" s="9">
         <v>46232.83601601852</v>
@@ -4301,16 +4304,16 @@
         <v>46240.8242518287</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I49" s="9">
         <v>46356</v>
@@ -4328,13 +4331,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4344,7 +4347,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B50" s="5">
         <v>46232.83611833333</v>
@@ -4354,7 +4357,7 @@
         <v>46233.641839375</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4378,7 +4381,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4391,7 +4394,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B51" s="9">
         <v>46232.836122465276</v>
@@ -4401,16 +4404,16 @@
         <v>46260.67989972222</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I51" s="9">
         <v>46293</v>
@@ -4428,13 +4431,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q51" s="9">
         <v>46294</v>
@@ -4454,7 +4457,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B52" s="5">
         <v>46232.83612731482</v>
@@ -4464,16 +4467,16 @@
         <v>46260.679925335644</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I52" s="5">
         <v>46293</v>
@@ -4491,13 +4494,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q52" s="5">
         <v>46294</v>
@@ -4517,7 +4520,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B53" s="9">
         <v>46232.83613222222</v>
@@ -4527,16 +4530,16 @@
         <v>46260.679949259254</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I53" s="9">
         <v>46293</v>
@@ -4554,13 +4557,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q53" s="9">
         <v>46294</v>
@@ -4580,7 +4583,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" s="5">
         <v>46232.836136909726</v>
@@ -4590,16 +4593,16 @@
         <v>46260.68020320602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I54" s="5">
         <v>46295</v>
@@ -4617,13 +4620,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q54" s="5">
         <v>46295</v>
@@ -4643,7 +4646,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B55" s="9">
         <v>46232.83614177084</v>
@@ -4653,16 +4656,16 @@
         <v>46260.6802031713</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I55" s="9">
         <v>46295</v>
@@ -4680,13 +4683,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q55" s="9">
         <v>46295</v>
@@ -4706,7 +4709,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B56" s="5">
         <v>46232.83614663195</v>
@@ -4716,16 +4719,16 @@
         <v>46260.68020337963</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I56" s="5">
         <v>46295</v>
@@ -4743,13 +4746,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q56" s="5">
         <v>46295</v>
@@ -4769,7 +4772,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B57" s="9">
         <v>46232.83615094908</v>
@@ -4779,7 +4782,7 @@
         <v>46233.64318932871</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4803,7 +4806,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4816,7 +4819,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B58" s="5">
         <v>46232.83615418982</v>
@@ -4832,10 +4835,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I58" s="5">
         <v>46296</v>
@@ -4853,13 +4856,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q58" s="5">
         <v>46304</v>
@@ -4879,7 +4882,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B59" s="9">
         <v>46232.83616251158</v>
@@ -4889,16 +4892,16 @@
         <v>46260.680265891206</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I59" s="9">
         <v>46307</v>
@@ -4916,13 +4919,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q59" s="9">
         <v>46324</v>
@@ -4942,7 +4945,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B60" s="5">
         <v>46232.83619825232</v>
@@ -4952,16 +4955,16 @@
         <v>46233.64356575231</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I60" s="5">
         <v>46307</v>
@@ -4979,13 +4982,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4995,7 +4998,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B61" s="9">
         <v>46232.8362028125</v>
@@ -5005,16 +5008,16 @@
         <v>46233.643566342595</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I61" s="9">
         <v>46307</v>
@@ -5032,13 +5035,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5048,7 +5051,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B62" s="5">
         <v>46232.83620730324</v>
@@ -5058,16 +5061,16 @@
         <v>46233.643566956016</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I62" s="5">
         <v>46307</v>
@@ -5085,13 +5088,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5101,7 +5104,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B63" s="9">
         <v>46232.83621217593</v>
@@ -5111,16 +5114,16 @@
         <v>46233.6435675463</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I63" s="9">
         <v>46307</v>
@@ -5138,13 +5141,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5154,7 +5157,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B64" s="5">
         <v>46232.836342152776</v>
@@ -5164,16 +5167,16 @@
         <v>46260.68039708333</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I64" s="5">
         <v>46325</v>
@@ -5191,13 +5194,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q64" s="5">
         <v>46328</v>
@@ -5217,7 +5220,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B65" s="9">
         <v>46232.83637209491</v>
@@ -5227,16 +5230,16 @@
         <v>46233.643859131946</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I65" s="9">
         <v>46325</v>
@@ -5254,13 +5257,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5270,7 +5273,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B66" s="5">
         <v>46232.836376666666</v>
@@ -5280,16 +5283,16 @@
         <v>46233.64385857639</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I66" s="5">
         <v>46325</v>
@@ -5307,13 +5310,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5323,7 +5326,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B67" s="9">
         <v>46232.836381319445</v>
@@ -5333,16 +5336,16 @@
         <v>46233.6438580324</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I67" s="9">
         <v>46325</v>
@@ -5360,13 +5363,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5376,7 +5379,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B68" s="5">
         <v>46232.83638501157</v>
@@ -5386,16 +5389,16 @@
         <v>46233.64385685185</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I68" s="5">
         <v>46325</v>
@@ -5413,13 +5416,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5429,7 +5432,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B69" s="9">
         <v>46232.836502499995</v>
@@ -5439,7 +5442,7 @@
         <v>46233.64467054398</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>25</v>
@@ -5463,7 +5466,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>26</v>
@@ -5476,7 +5479,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B70" s="5">
         <v>46232.83650636574</v>
@@ -5486,16 +5489,16 @@
         <v>46260.68082252315</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I70" s="5">
         <v>46239</v>
@@ -5513,13 +5516,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>54</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q70" s="5">
         <v>46240</v>
@@ -5534,12 +5537,12 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B71" s="9">
         <v>46232.836519247685</v>
@@ -5549,16 +5552,16 @@
         <v>46260.68090866898</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I71" s="9">
         <v>46239</v>
@@ -5576,13 +5579,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>59</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q71" s="9">
         <v>46240</v>
@@ -5602,7 +5605,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B72" s="5">
         <v>46232.83652788194</v>
@@ -5612,16 +5615,16 @@
         <v>46260.680964652776</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I72" s="5">
         <v>46343</v>
@@ -5639,13 +5642,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q72" s="5">
         <v>46344</v>
@@ -5665,7 +5668,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B73" s="9">
         <v>46232.83654054398</v>
@@ -5675,7 +5678,7 @@
         <v>46233.645743333334</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>25</v>
@@ -5699,7 +5702,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5712,7 +5715,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B74" s="5">
         <v>46232.83654375</v>
@@ -5722,7 +5725,7 @@
         <v>46260.68063219907</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5749,13 +5752,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q74" s="5">
         <v>46346</v>
@@ -5775,7 +5778,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B75" s="9">
         <v>46232.836570162035</v>
@@ -5785,7 +5788,7 @@
         <v>46233.65450737269</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5812,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5828,7 +5831,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B76" s="5">
         <v>46232.83657339121</v>
@@ -5838,7 +5841,7 @@
         <v>46260.680678715275</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5865,13 +5868,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5881,7 +5884,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B77" s="9">
         <v>46232.83657665509</v>
@@ -5891,7 +5894,7 @@
         <v>46233.65449428241</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5918,13 +5921,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5934,7 +5937,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B78" s="5">
         <v>46232.83658011574</v>
@@ -5944,7 +5947,7 @@
         <v>46233.65449056713</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5971,13 +5974,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5987,7 +5990,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B79" s="9">
         <v>46232.83664298611</v>
@@ -5997,7 +6000,7 @@
         <v>46260.681952962965</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6024,13 +6027,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q79" s="9">
         <v>46349</v>
@@ -6050,7 +6053,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B80" s="5">
         <v>46232.8367334375</v>
@@ -6060,7 +6063,7 @@
         <v>46233.65465295139</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6087,13 +6090,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6103,7 +6106,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B81" s="9">
         <v>46232.83673865741</v>
@@ -6113,7 +6116,7 @@
         <v>46233.65464978009</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6140,13 +6143,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6156,7 +6159,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B82" s="5">
         <v>46232.83674337963</v>
@@ -6166,7 +6169,7 @@
         <v>46233.65464680556</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6193,13 +6196,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6209,7 +6212,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B83" s="9">
         <v>46232.83674840278</v>
@@ -6219,7 +6222,7 @@
         <v>46233.65464278935</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6246,13 +6249,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6262,7 +6265,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B84" s="5">
         <v>46232.836891377316</v>
@@ -6272,7 +6275,7 @@
         <v>46260.68198707176</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6299,13 +6302,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q84" s="5">
         <v>46350</v>
@@ -6325,7 +6328,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B85" s="9">
         <v>46232.836924375</v>
@@ -6335,7 +6338,7 @@
         <v>46233.65478820602</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6362,13 +6365,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6378,7 +6381,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B86" s="5">
         <v>46232.836927488424</v>
@@ -6388,7 +6391,7 @@
         <v>46233.65478517361</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6415,13 +6418,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6431,7 +6434,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B87" s="9">
         <v>46232.836930474536</v>
@@ -6441,7 +6444,7 @@
         <v>46233.654781273144</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6468,13 +6471,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6484,7 +6487,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B88" s="5">
         <v>46232.836933530096</v>
@@ -6494,7 +6497,7 @@
         <v>46233.65477793981</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6521,13 +6524,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6537,7 +6540,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B89" s="9">
         <v>46232.836990428244</v>
@@ -6547,7 +6550,7 @@
         <v>46260.68201387732</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6574,13 +6577,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q89" s="9">
         <v>46351</v>
@@ -6600,7 +6603,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B90" s="5">
         <v>46232.83702368056</v>
@@ -6610,7 +6613,7 @@
         <v>46233.65523672454</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6637,13 +6640,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6653,7 +6656,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B91" s="9">
         <v>46232.837026863424</v>
@@ -6663,7 +6666,7 @@
         <v>46233.655233032405</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6690,13 +6693,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6706,7 +6709,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B92" s="5">
         <v>46232.83702931713</v>
@@ -6716,7 +6719,7 @@
         <v>46233.655229537035</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6743,13 +6746,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6759,7 +6762,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B93" s="9">
         <v>46232.83703243056</v>
@@ -6769,7 +6772,7 @@
         <v>46233.655226435185</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6796,13 +6799,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6812,7 +6815,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B94" s="5">
         <v>46232.83713237269</v>
@@ -6822,7 +6825,7 @@
         <v>46260.682038240746</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6849,13 +6852,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q94" s="5">
         <v>46352</v>
@@ -6875,7 +6878,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B95" s="9">
         <v>46232.83715663194</v>
@@ -6885,7 +6888,7 @@
         <v>46233.655363067126</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6912,13 +6915,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6928,7 +6931,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B96" s="5">
         <v>46232.83715961805</v>
@@ -6938,7 +6941,7 @@
         <v>46233.65535960648</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6965,13 +6968,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6981,7 +6984,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B97" s="9">
         <v>46232.83716207176</v>
@@ -6991,7 +6994,7 @@
         <v>46233.65535680555</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7018,13 +7021,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7034,7 +7037,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B98" s="5">
         <v>46232.837165324076</v>
@@ -7044,7 +7047,7 @@
         <v>46233.65534453704</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7071,13 +7074,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7087,7 +7090,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B99" s="9">
         <v>46232.837259120366</v>
@@ -7097,7 +7100,7 @@
         <v>46260.68206168982</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7124,10 +7127,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7150,7 +7153,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B100" s="5">
         <v>46232.837293495366</v>
@@ -7160,7 +7163,7 @@
         <v>46233.655496747684</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7187,13 +7190,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7203,7 +7206,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B101" s="9">
         <v>46232.83729747686</v>
@@ -7213,7 +7216,7 @@
         <v>46233.65549366898</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7240,13 +7243,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7256,7 +7259,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B102" s="5">
         <v>46232.83730121527</v>
@@ -7266,7 +7269,7 @@
         <v>46233.65549012732</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7293,13 +7296,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7309,7 +7312,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B103" s="9">
         <v>46232.83730554398</v>
@@ -7319,7 +7322,7 @@
         <v>46233.65548677083</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7346,13 +7349,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7362,7 +7365,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B104" s="5">
         <v>46232.83737395833</v>
@@ -7372,7 +7375,7 @@
         <v>46260.68208619213</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7399,10 +7402,10 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>26</v>
@@ -7425,7 +7428,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B105" s="9">
         <v>46232.83744990741</v>
@@ -7435,7 +7438,7 @@
         <v>46233.65578177084</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7462,13 +7465,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7478,7 +7481,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B106" s="5">
         <v>46232.83745327547</v>
@@ -7488,7 +7491,7 @@
         <v>46233.65578223379</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7515,13 +7518,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7531,7 +7534,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B107" s="9">
         <v>46232.837456712965</v>
@@ -7541,7 +7544,7 @@
         <v>46233.65578273148</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7568,13 +7571,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7584,7 +7587,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B108" s="5">
         <v>46232.83746033565</v>
@@ -7594,7 +7597,7 @@
         <v>46233.65578320602</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7621,13 +7624,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7637,7 +7640,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B109" s="9">
         <v>46232.837520092595</v>
@@ -7647,7 +7650,7 @@
         <v>46233.64911908565</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>25</v>
@@ -7671,7 +7674,7 @@
         <v>26</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>26</v>
@@ -7684,7 +7687,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B110" s="5">
         <v>46232.837524166665</v>
@@ -7694,16 +7697,16 @@
         <v>46260.68212885417</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I110" s="5">
         <v>46359</v>
@@ -7721,13 +7724,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q110" s="5">
         <v>46359</v>
@@ -7747,7 +7750,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B111" s="9">
         <v>46232.83755571759</v>
@@ -7757,16 +7760,16 @@
         <v>46233.65598135417</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I111" s="9">
         <v>46359</v>
@@ -7784,13 +7787,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7800,7 +7803,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B112" s="5">
         <v>46232.837559548614</v>
@@ -7810,16 +7813,16 @@
         <v>46233.65597814815</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I112" s="5">
         <v>46359</v>
@@ -7837,13 +7840,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7853,7 +7856,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B113" s="9">
         <v>46232.83756364584</v>
@@ -7863,16 +7866,16 @@
         <v>46233.65597451389</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I113" s="9">
         <v>46359</v>
@@ -7890,13 +7893,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7906,7 +7909,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B114" s="5">
         <v>46232.83756778935</v>
@@ -7916,16 +7919,16 @@
         <v>46233.65597096065</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I114" s="5">
         <v>46359</v>
@@ -7943,13 +7946,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -7959,7 +7962,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B115" s="9">
         <v>46232.83768009259</v>
@@ -7969,7 +7972,7 @@
         <v>46260.68216930555</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -7996,10 +7999,10 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>26</v>
@@ -8022,7 +8025,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B116" s="5">
         <v>46232.837703680554</v>
@@ -8032,7 +8035,7 @@
         <v>46233.656983611116</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8059,13 +8062,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8075,7 +8078,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B117" s="9">
         <v>46232.837707175924</v>
@@ -8085,7 +8088,7 @@
         <v>46233.65698048611</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8112,13 +8115,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8128,7 +8131,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B118" s="5">
         <v>46232.837710555556</v>
@@ -8138,7 +8141,7 @@
         <v>46233.65697711805</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8165,13 +8168,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8181,7 +8184,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B119" s="9">
         <v>46232.837713981484</v>
@@ -8191,7 +8194,7 @@
         <v>46233.65697394676</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8218,13 +8221,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8234,7 +8237,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B120" s="5">
         <v>46232.837813125</v>
@@ -8244,16 +8247,16 @@
         <v>46260.68218884259</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I120" s="5">
         <v>46363</v>
@@ -8271,13 +8274,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q120" s="5">
         <v>46363</v>
@@ -8297,7 +8300,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B121" s="9">
         <v>46232.83784550926</v>
@@ -8307,16 +8310,16 @@
         <v>46233.65710880787</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I121" s="9">
         <v>46363</v>
@@ -8334,13 +8337,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8350,7 +8353,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B122" s="5">
         <v>46232.837850254626</v>
@@ -8360,16 +8363,16 @@
         <v>46233.65710540509</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I122" s="5">
         <v>46363</v>
@@ -8387,13 +8390,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8403,7 +8406,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B123" s="9">
         <v>46232.83785502314</v>
@@ -8413,16 +8416,16 @@
         <v>46233.657102268524</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I123" s="9">
         <v>46363</v>
@@ -8440,13 +8443,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8456,7 +8459,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B124" s="5">
         <v>46232.83785935185</v>
@@ -8466,16 +8469,16 @@
         <v>46233.65709878472</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I124" s="5">
         <v>46363</v>
@@ -8493,13 +8496,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8509,7 +8512,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B125" s="9">
         <v>46232.837973483794</v>
@@ -8519,16 +8522,16 @@
         <v>46260.682238113426</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I125" s="9">
         <v>46364</v>
@@ -8546,13 +8549,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q125" s="9">
         <v>46364</v>
@@ -8572,7 +8575,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B126" s="5">
         <v>46232.838005439815</v>
@@ -8582,16 +8585,16 @@
         <v>46233.65729934028</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I126" s="5">
         <v>46364</v>
@@ -8609,13 +8612,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8625,7 +8628,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B127" s="9">
         <v>46232.838009259256</v>
@@ -8635,16 +8638,16 @@
         <v>46233.65729582176</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I127" s="9">
         <v>46364</v>
@@ -8662,13 +8665,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8678,7 +8681,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B128" s="5">
         <v>46232.83801302083</v>
@@ -8688,16 +8691,16 @@
         <v>46233.657292557866</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I128" s="5">
         <v>46364</v>
@@ -8715,13 +8718,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8731,7 +8734,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B129" s="9">
         <v>46232.83801685185</v>
@@ -8741,16 +8744,16 @@
         <v>46233.65728900463</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I129" s="9">
         <v>46364</v>
@@ -8768,13 +8771,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8784,7 +8787,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B130" s="5">
         <v>46232.83807947917</v>
@@ -8794,7 +8797,7 @@
         <v>46233.65049251157</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>25</v>
@@ -8818,7 +8821,7 @@
         <v>26</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>26</v>
@@ -8831,7 +8834,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B131" s="9">
         <v>46232.83808368056</v>
@@ -8841,16 +8844,16 @@
         <v>46260.68180542824</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I131" s="9">
         <v>46365</v>
@@ -8868,13 +8871,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q131" s="9">
         <v>46373</v>
@@ -8894,7 +8897,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B132" s="5">
         <v>46232.83812608796</v>
@@ -8904,16 +8907,16 @@
         <v>46260.68180643518</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I132" s="5">
         <v>46365</v>
@@ -8931,13 +8934,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q132" s="5">
         <v>46373</v>
